--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
@@ -1743,7 +1743,7 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>123</v>
@@ -2262,7 +2262,7 @@
         <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>123</v>
@@ -2781,7 +2781,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -2989,7 +2989,7 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>123</v>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
